--- a/data/trans_orig/IP07C02-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07C02-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido correr bien en 2007 (tasa de respuesta: 89,79%)</t>
+          <t>Menores según la frecuencia de haber podido correr bien en 2007 (tasa de respuesta: 89,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52199</t>
+          <t>52389</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>68910</t>
+          <t>68881</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>61,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>55880</t>
+          <t>56085</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>73371</t>
+          <t>73513</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>113166</t>
+          <t>112481</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>136026</t>
+          <t>136578</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>58,07%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35786</t>
+          <t>35355</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52242</t>
+          <t>52399</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>46,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>44392</t>
+          <t>43997</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62465</t>
+          <t>61433</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>86075</t>
+          <t>85665</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>109449</t>
+          <t>109613</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>46,61%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>2038</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9254</t>
+          <t>9039</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>648</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6354</t>
+          <t>6103</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3844</t>
+          <t>3984</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12492</t>
+          <t>13411</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>655</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6631</t>
+          <t>6096</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>591</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5480</t>
+          <t>5273</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>8561</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4657</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4612</t>
+          <t>4066</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>84093</t>
+          <t>83030</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>103908</t>
+          <t>103965</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>99070</t>
+          <t>100279</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>120038</t>
+          <t>121362</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>54,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>188722</t>
+          <t>187846</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>218785</t>
+          <t>218710</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>59,99%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>64293</t>
+          <t>64886</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>85492</t>
+          <t>85713</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>57630</t>
+          <t>57383</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>78409</t>
+          <t>77618</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>127867</t>
+          <t>127436</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>157437</t>
+          <t>157583</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>43,23%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4542</t>
+          <t>4562</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13608</t>
+          <t>13656</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2550</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9824</t>
+          <t>9783</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8667</t>
+          <t>8394</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>20594</t>
+          <t>19836</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>635</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5422</t>
+          <t>5367</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4022</t>
+          <t>3969</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7429</t>
+          <t>7219</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4446</t>
+          <t>4382</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4608</t>
+          <t>5208</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>140579</t>
+          <t>140317</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>167289</t>
+          <t>167296</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>161542</t>
+          <t>160156</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>188731</t>
+          <t>188347</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>51,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>309188</t>
+          <t>308857</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>347401</t>
+          <t>349109</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>58,21%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>105469</t>
+          <t>106491</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>132490</t>
+          <t>132864</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>108056</t>
+          <t>107134</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>133371</t>
+          <t>135640</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>220219</t>
+          <t>219773</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>259538</t>
+          <t>258693</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>43,13%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8289</t>
+          <t>7884</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19622</t>
+          <t>20017</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4503</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13134</t>
+          <t>13155</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>14957</t>
+          <t>14592</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>29815</t>
+          <t>29662</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>9382</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7459</t>
+          <t>8123</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4287</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13567</t>
+          <t>13596</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>679</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5886</t>
+          <t>6032</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>681</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6184</t>
+          <t>6405</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido correr bien en 2012 (tasa de respuesta: 95,62%)</t>
+          <t>Menores según la frecuencia de haber podido correr bien en 2012 (tasa de respuesta: 95,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>50255</t>
+          <t>50432</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>68849</t>
+          <t>69977</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>70996</t>
+          <t>71130</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>90696</t>
+          <t>91589</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>125609</t>
+          <t>125815</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>154881</t>
+          <t>154889</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71303</t>
+          <t>70735</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>90496</t>
+          <t>91487</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>61,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57805</t>
+          <t>56921</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>76997</t>
+          <t>77172</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>133628</t>
+          <t>134312</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>162495</t>
+          <t>161980</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>53,16%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2958</t>
+          <t>3041</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11441</t>
+          <t>12148</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2686</t>
+          <t>2825</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10641</t>
+          <t>11007</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7994</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19303</t>
+          <t>18945</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3998</t>
+          <t>4497</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3185</t>
+          <t>2865</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>4801</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>3894</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3415</t>
+          <t>4115</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>427</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5728</t>
+          <t>5717</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44003</t>
+          <t>44313</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64999</t>
+          <t>65104</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>75021</t>
+          <t>75328</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>96540</t>
+          <t>96813</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>56,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>127238</t>
+          <t>125863</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>155758</t>
+          <t>154729</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>46,49%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78567</t>
+          <t>78809</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>100299</t>
+          <t>100277</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61861</t>
+          <t>61580</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>82328</t>
+          <t>83147</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>146366</t>
+          <t>145982</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>174305</t>
+          <t>174888</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>52,54%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9541</t>
+          <t>9737</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23003</t>
+          <t>22535</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3205</t>
+          <t>3151</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11680</t>
+          <t>11655</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>14722</t>
+          <t>14932</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>28963</t>
+          <t>30511</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>636</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5277</t>
+          <t>6507</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>1887</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8623</t>
+          <t>9454</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3198</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10768</t>
+          <t>11226</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3025</t>
+          <t>3721</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>696</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6695</t>
+          <t>6764</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7996</t>
+          <t>6953</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>100975</t>
+          <t>102073</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>128185</t>
+          <t>128628</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>153952</t>
+          <t>152094</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>183145</t>
+          <t>181991</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,05%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>261726</t>
+          <t>260549</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>304775</t>
+          <t>301516</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>47,29%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>155319</t>
+          <t>154998</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>183507</t>
+          <t>183156</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>124779</t>
+          <t>123763</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>153081</t>
+          <t>153192</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>287343</t>
+          <t>289336</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>329999</t>
+          <t>329930</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,75%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14718</t>
+          <t>15427</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>30123</t>
+          <t>30590</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7688</t>
+          <t>7574</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19095</t>
+          <t>18284</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>24214</t>
+          <t>25792</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>44458</t>
+          <t>43700</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>934</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7475</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2036</t>
+          <t>2039</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9549</t>
+          <t>9795</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4171</t>
+          <t>4396</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13706</t>
+          <t>13701</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>430</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4477</t>
+          <t>4507</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8394</t>
+          <t>8018</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2403</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10359</t>
+          <t>9568</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido correr bien en 2016 (tasa de respuesta: 95,67%)</t>
+          <t>Menores según la frecuencia de haber podido correr bien en 2016 (tasa de respuesta: 95,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5284,12 +5284,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>111239</t>
+          <t>111456</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>131154</t>
+          <t>131303</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5299,12 +5299,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>104607</t>
+          <t>104772</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>125392</t>
+          <t>125303</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>58,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>222327</t>
+          <t>219801</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>250763</t>
+          <t>250340</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>69,77%</t>
         </is>
       </c>
     </row>
@@ -5397,12 +5397,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43657</t>
+          <t>43737</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63153</t>
+          <t>63386</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5412,12 +5412,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45738</t>
+          <t>45289</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>66540</t>
+          <t>66530</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>94233</t>
+          <t>96014</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>122822</t>
+          <t>125197</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,89%</t>
         </is>
       </c>
     </row>
@@ -5510,12 +5510,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7698</t>
+          <t>7588</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2475</t>
+          <t>2543</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10343</t>
+          <t>10824</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4617</t>
+          <t>4591</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14622</t>
+          <t>14588</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3426</t>
+          <t>3405</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>652</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5750</t>
+          <t>6609</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>728</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6824</t>
+          <t>6502</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5058</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>79098</t>
+          <t>79377</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>101206</t>
+          <t>101015</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>48,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>87455</t>
+          <t>88396</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>109604</t>
+          <t>110366</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>174887</t>
+          <t>175709</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>205993</t>
+          <t>204860</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>61,08%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54401</t>
+          <t>55121</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>75684</t>
+          <t>76176</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48052</t>
+          <t>47425</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>69016</t>
+          <t>68498</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>108326</t>
+          <t>108078</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>137713</t>
+          <t>136958</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>40,83%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3624</t>
+          <t>3468</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12731</t>
+          <t>13329</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4439</t>
+          <t>4184</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13685</t>
+          <t>13722</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>9997</t>
+          <t>10219</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>22977</t>
+          <t>24289</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4280</t>
+          <t>4759</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>736</t>
+          <t>728</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7097</t>
+          <t>7022</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9247</t>
+          <t>9194</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3865</t>
+          <t>3148</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>579</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5290</t>
+          <t>5823</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6468,12 +6468,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>708</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6631</t>
+          <t>6759</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>198260</t>
+          <t>197602</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>227854</t>
+          <t>225683</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>199001</t>
+          <t>200208</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>229629</t>
+          <t>229570</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>405306</t>
+          <t>404043</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>447615</t>
+          <t>447020</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>64,39%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>102122</t>
+          <t>103931</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>131084</t>
+          <t>132564</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>100066</t>
+          <t>100008</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>129284</t>
+          <t>126966</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>211836</t>
+          <t>211069</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>252046</t>
+          <t>251865</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,28%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6277</t>
+          <t>6268</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17379</t>
+          <t>17020</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8362</t>
+          <t>8918</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20963</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>17353</t>
+          <t>16486</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>33159</t>
+          <t>32673</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -6987,12 +6987,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>619</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5449</t>
+          <t>5493</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2293</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10686</t>
+          <t>9770</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7037,12 +7037,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3567</t>
+          <t>3512</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12884</t>
+          <t>12517</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7077,7 +7077,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -7100,12 +7100,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>618</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5724</t>
+          <t>6163</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>586</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5992</t>
+          <t>5710</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8489</t>
+          <t>9051</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7185,12 +7185,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP07C02-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07C02-Edad-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de haber podido correr bien en 2007 (tasa de respuesta: 89,79%)</t>
+          <t>Menores según la frecuencia de haber podido correr bien, percibida por el/la menor [KIDSCREEN 20] en 2007 (tasa de respuesta: 89,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>64504</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>56679</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>73940</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>52,24%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>45,9%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>59,88%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>60497</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>52389</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>68881</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>51492</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>68433</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>54,15%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>46,9%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>61,66%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>64504</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>56085</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>73513</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>52,24%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>112481</t>
+          <t>113929</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>136578</t>
+          <t>138206</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>58,76%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>53060</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>43462</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>61470</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>42,97%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>35,2%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>49,78%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>43773</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>35355</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>52399</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>36215</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>52373</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>39,18%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>31,65%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>46,91%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>53060</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>43997</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>61433</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>42,97%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>85665</t>
+          <t>84435</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>109613</t>
+          <t>107741</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>45,81%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2658</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>6435</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>5,21%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>4826</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2038</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>9039</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2063</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>9395</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>4,32%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>8,09%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2658</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>648</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>6103</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3984</t>
+          <t>3993</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13411</t>
+          <t>12862</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -1061,72 +1061,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>595</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5524</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,47%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>2615</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>655</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6096</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6087</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,34%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,46%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1991</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5273</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8561</t>
+          <t>9134</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -1174,107 +1174,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1268</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3821</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>3,09%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>1268</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>4212</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>4580</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>3,41%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1268</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>4066</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>123481</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>123481</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>123481</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>111711</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>111711</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>111711</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>123481</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>123481</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>123481</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>110391</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>100199</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>121649</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>59,47%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>53,98%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>65,54%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>93533</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>83030</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>103965</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>83665</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>105574</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>52,27%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>46,4%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>58,1%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>110391</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>100279</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>121362</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>59,47%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>59,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>187846</t>
+          <t>188362</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>218710</t>
+          <t>219601</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>60,24%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>67348</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>56221</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>78184</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>36,28%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>30,29%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>42,12%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>111</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>75133</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>64886</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>85713</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>64136</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>85296</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>41,99%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>36,26%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>47,9%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>67348</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>57383</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>77618</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>36,28%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>127436</t>
+          <t>127587</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>157583</t>
+          <t>156723</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>42,99%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5237</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2550</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>9572</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>5,16%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>8257</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>4562</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>13656</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>4646</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>13821</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>4,61%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>7,63%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>5237</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>2550</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>9783</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8394</t>
+          <t>8148</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19836</t>
+          <t>20152</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -1743,72 +1743,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1323</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4710</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,54%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>635</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5367</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>629</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5329</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,12%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,35%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,0%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1323</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3969</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7219</t>
+          <t>7441</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -1856,107 +1856,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1314</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4581</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2,47%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>1314</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>4382</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>4537</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>2,36%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1314</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>5208</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>185614</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>185614</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>185614</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>264</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>178935</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>178935</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>178935</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>185614</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>185614</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>185614</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>174895</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>159976</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>188693</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>56,58%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>51,76%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>61,05%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>154030</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>140317</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>167296</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>140383</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>167669</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>53,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>48,28%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>57,56%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>266</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>174895</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>160156</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>188347</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>56,58%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>308857</t>
+          <t>309894</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>349109</t>
+          <t>346449</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>57,77%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>120408</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>107410</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>136026</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>38,96%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>34,75%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>44,01%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>177</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>118906</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>106491</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>132864</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>105088</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>132372</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>40,91%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>36,64%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>45,71%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>120408</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>107134</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>135640</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>38,96%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>219773</t>
+          <t>221762</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>258693</t>
+          <t>258673</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2312,72 +2312,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>7895</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>3969</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>13061</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>4,23%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>13083</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>7884</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>20017</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>8235</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>20085</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>4,5%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>2,71%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>6,89%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>7895</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>4479</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>13155</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>14592</t>
+          <t>13985</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>29662</t>
+          <t>29019</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -2425,72 +2425,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3315</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1281</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>7261</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>4627</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1992</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>9382</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>2042</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>9335</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,59%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>3,23%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>3315</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>1271</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>8123</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3936</t>
+          <t>4466</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13596</t>
+          <t>14021</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -2538,92 +2538,92 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2582</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>693</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>6357</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>2582</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>679</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>6032</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>2582</t>
-        </is>
-      </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>680</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6405</t>
+          <t>6550</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>465</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>309095</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>309095</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>309095</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>432</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>290646</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>290646</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>290646</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>465</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>309095</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>309095</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>309095</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2813,13 +2813,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de haber podido correr bien en 2012 (tasa de respuesta: 95,62%)</t>
+          <t>Menores según la frecuencia de haber podido correr bien, percibida por el/la menor [KIDSCREEN 20] en 2012 (tasa de respuesta: 95,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2830,7 +2830,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2998,72 +2998,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>80999</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>71629</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>90705</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>52,11%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>46,09%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>58,36%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>59782</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>50432</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>69977</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>49797</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>69755</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>40,04%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>33,78%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>46,87%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>80999</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>71130</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>91589</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>52,11%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>125815</t>
+          <t>127320</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>154889</t>
+          <t>155455</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>51,02%</t>
         </is>
       </c>
     </row>
@@ -3111,72 +3111,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>67069</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>56973</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>76888</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>43,15%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>36,66%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>49,47%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>113</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>80596</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>70735</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>91487</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>70422</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>91360</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>53,99%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>47,38%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>61,28%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>67069</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>56921</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>77172</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>43,15%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>134312</t>
+          <t>132653</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>161980</t>
+          <t>161646</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>53,05%</t>
         </is>
       </c>
     </row>
@@ -3229,67 +3229,67 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>5972</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2942</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>10914</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>3,84%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>7,02%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>6600</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>3041</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>12148</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>3134</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>12053</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>4,42%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>8,14%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>5972</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2825</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>11007</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>3,84%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7994</t>
+          <t>7574</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>18945</t>
+          <t>18657</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -3337,72 +3337,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2819</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1287</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4497</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4525</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,86%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>564</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2865</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>566</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4801</t>
+          <t>4655</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -3450,72 +3450,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4112</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>1024</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3894</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3974</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,69%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,61%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>823</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>4115</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>430</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5717</t>
+          <t>5027</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -3563,57 +3563,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>155427</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>155427</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>155427</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>149289</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>149289</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>149289</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>155427</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>155427</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>155427</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3680,72 +3680,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>86414</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>74874</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>96807</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>50,43%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>43,7%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>56,5%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>54408</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>44313</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>65104</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>45246</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>65394</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>33,69%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>27,44%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>40,31%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>86414</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>75328</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>96813</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>50,43%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>125863</t>
+          <t>126901</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>154729</t>
+          <t>156628</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>47,06%</t>
         </is>
       </c>
     </row>
@@ -3793,72 +3793,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>71666</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>61672</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>82555</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>41,83%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>35,99%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>48,18%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>89669</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>78809</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>100277</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>78954</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>100170</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>55,52%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>48,8%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>62,09%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>71666</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>61580</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>83147</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>41,83%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>145982</t>
+          <t>146337</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>174888</t>
+          <t>176199</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>52,94%</t>
         </is>
       </c>
     </row>
@@ -3906,72 +3906,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>6344</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3090</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>11449</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3,7%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>6,68%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>14820</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>9737</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>22535</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>9519</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>22664</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>9,18%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>6,03%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>13,95%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>6344</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>3151</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>11655</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>3,7%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>14932</t>
+          <t>14151</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>30511</t>
+          <t>29528</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -4019,72 +4019,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4246</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1406</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8493</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,48%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,96%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1954</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>636</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6507</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>635</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5280</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,21%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,39%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,03%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>4246</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1887</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>9454</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>2967</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11226</t>
+          <t>11423</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -4132,72 +4132,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2669</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>671</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6263</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3,66%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>656</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3721</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3503</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,41%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>2669</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>696</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>6764</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6953</t>
+          <t>7267</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -4245,57 +4245,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>171339</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>171339</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>171339</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>161508</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>161508</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>161508</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>171339</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>171339</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>171339</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4362,72 +4362,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>167413</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>153006</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>182003</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>51,23%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>46,82%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>55,7%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>114190</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>102073</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>128628</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>100517</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>128733</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>36,74%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>32,84%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>41,39%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>167413</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>152094</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>181991</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>51,23%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>260549</t>
+          <t>261801</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>301516</t>
+          <t>303067</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>47,54%</t>
         </is>
       </c>
     </row>
@@ -4475,72 +4475,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>138735</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>124001</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>153217</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>42,46%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>37,95%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>46,89%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>170266</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>154998</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>183156</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>154883</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>184547</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>54,78%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>49,87%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>58,93%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>138735</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>123763</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>153192</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>42,46%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>289336</t>
+          <t>287594</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>329930</t>
+          <t>329349</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>51,66%</t>
         </is>
       </c>
     </row>
@@ -4588,72 +4588,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>12316</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>7762</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>19109</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3,77%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2,38%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>5,85%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>21420</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>15427</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>30590</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>14566</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>29263</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>6,89%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>4,96%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>9,84%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>12316</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>7574</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>18284</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>3,77%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>25792</t>
+          <t>25010</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>43700</t>
+          <t>44921</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -4701,72 +4701,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>4810</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2127</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>9999</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>3,06%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>3241</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>7155</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>1265</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>6915</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,04%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>4810</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>2039</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>9795</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4396</t>
+          <t>4344</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13701</t>
+          <t>13981</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -4814,72 +4814,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3492</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1324</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>7686</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>1680</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>430</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4507</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>426</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>4570</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,54%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,14%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>3492</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>1318</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>8018</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9568</t>
+          <t>9788</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -4927,57 +4927,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>475</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>326766</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>326766</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>326766</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>442</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>310798</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>310798</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>310798</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>475</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>326766</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>326766</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>326766</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5089,13 +5089,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de haber podido correr bien en 2016 (tasa de respuesta: 95,67%)</t>
+          <t>Menores según la frecuencia de haber podido correr bien, percibida por el/la menor [KIDSCREEN 20] en 2016 (tasa de respuesta: 95,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5106,7 +5106,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5274,72 +5274,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>115432</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>105229</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>125195</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>64,63%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>58,91%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>70,09%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>173</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>121786</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>111456</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>131303</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>111429</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>132163</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>67,59%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>61,86%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>72,88%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>115432</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>104772</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>125303</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>64,63%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>219801</t>
+          <t>223644</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>250340</t>
+          <t>251562</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>70,11%</t>
         </is>
       </c>
     </row>
@@ -5387,72 +5387,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>55613</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>45854</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>65752</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>31,14%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>25,67%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>36,81%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>53065</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>43737</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>63386</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>42897</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>63053</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>29,45%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>24,28%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>35,18%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>55613</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>45289</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>66530</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>31,14%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>96014</t>
+          <t>94964</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>125197</t>
+          <t>122137</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,04%</t>
         </is>
       </c>
     </row>
@@ -5500,72 +5500,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5425</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2572</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>10476</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>3,04%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>5,87%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>3298</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1276</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7588</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>7604</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>1,83%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>4,21%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>5425</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2543</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>10824</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>3,04%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4591</t>
+          <t>4956</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14588</t>
+          <t>14979</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -5613,72 +5613,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2142</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6393</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,58%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>617</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3405</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2824</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2142</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6609</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6502</t>
+          <t>7100</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -5726,107 +5726,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>1409</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5176</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5261</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,78%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,87%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>2,92%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1409</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>5210</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1409</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>4715</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -5839,57 +5839,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>178611</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>178611</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>178611</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>180175</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>180175</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>180175</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>178611</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>178611</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>178611</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5956,72 +5956,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>99238</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>88006</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>110646</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>58,17%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>51,59%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>64,86%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>90907</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>79377</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>101015</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>80087</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>101620</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>55,16%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>48,16%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>61,29%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>99238</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>88396</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>110366</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>58,17%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>61,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>175709</t>
+          <t>174985</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>204860</t>
+          <t>205359</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>61,23%</t>
         </is>
       </c>
     </row>
@@ -6069,72 +6069,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>58060</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>47732</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>67964</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>34,03%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>27,98%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>39,84%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>64572</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>55121</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>76176</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>54148</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>75087</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>39,18%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>33,45%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>46,22%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>58060</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>47425</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>68498</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>34,03%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>108078</t>
+          <t>108259</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>136958</t>
+          <t>137798</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>41,08%</t>
         </is>
       </c>
     </row>
@@ -6182,72 +6182,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>8229</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4136</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>14315</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>4,82%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>8,39%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>7310</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>3468</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>13329</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>3954</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>13263</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>4,44%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>8,09%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>8229</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>4184</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>13722</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>4,82%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10219</t>
+          <t>10132</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>24289</t>
+          <t>23877</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -6295,72 +6295,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2996</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7268</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,26%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1391</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4759</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4942</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,84%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,89%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2996</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>728</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7022</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>1515</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9194</t>
+          <t>8661</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -6408,72 +6408,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2070</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>585</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5270</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1,21%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3,09%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>626</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3148</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3094</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,38%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,91%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>2070</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>579</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>5823</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>712</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6759</t>
+          <t>6494</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -6521,57 +6521,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>170592</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>170592</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>170592</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>164807</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>164807</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>164807</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>170592</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>170592</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>170592</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6638,72 +6638,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>214670</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>198893</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>229727</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>61,47%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>56,96%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>65,79%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>300</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>212694</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>197602</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>225683</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>197067</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>226682</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>61,65%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>57,28%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>65,42%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>294</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>214670</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>200208</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>229570</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>61,47%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,33%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>404043</t>
+          <t>407703</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>447020</t>
+          <t>447838</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>64,51%</t>
         </is>
       </c>
     </row>
@@ -6751,72 +6751,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>113672</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>100406</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>128273</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>32,55%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>28,75%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>36,73%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>117637</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>103931</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>132564</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>102672</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>132778</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>34,1%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>30,13%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>38,43%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>113672</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>100008</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>126966</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>32,55%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>211069</t>
+          <t>210733</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>251865</t>
+          <t>251054</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,17%</t>
         </is>
       </c>
     </row>
@@ -6864,92 +6864,92 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>13653</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>8574</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>20605</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3,91%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>5,9%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>10608</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>6268</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>5795</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>16401</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>4,75%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>24261</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
         <is>
           <t>17020</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>3,07%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>4,93%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>13653</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>8918</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>20963</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>3,91%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>6,0%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>24261</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>16486</t>
-        </is>
-      </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>32673</t>
+          <t>32925</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -6977,72 +6977,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>5138</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2090</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>10664</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>3,05%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>2009</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>619</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>5493</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5839</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,58%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,18%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>5138</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>2150</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>9770</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3512</t>
+          <t>3517</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12517</t>
+          <t>12275</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7077,7 +7077,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -7095,102 +7095,102 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>2070</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>583</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>5517</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
           <t>2035</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>618</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>6163</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>6017</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,59%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,18%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>2070</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>586</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>5710</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>1421</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>8305</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>0,59%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>4105</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>1516</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>9051</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -7203,57 +7203,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>349203</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>349203</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>349203</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>492</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>344983</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>344983</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>344983</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>349203</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>349203</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>349203</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
